--- a/NECP Scenario/Results/Regional Results/EL62_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL62_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547323571564688E-12</v>
+        <v>2.284564023388668E-12</v>
       </c>
       <c r="C2">
-        <v>8.102393907326599E-13</v>
+        <v>1.196285522518191E-12</v>
       </c>
       <c r="D2">
-        <v>1.190475105185057E-12</v>
+        <v>1.757692177212448E-12</v>
       </c>
       <c r="E2">
-        <v>1.749231388227161E-12</v>
+        <v>2.582674415698408E-12</v>
       </c>
       <c r="F2">
-        <v>2.570219105803827E-12</v>
+        <v>3.794833166864456E-12</v>
       </c>
       <c r="G2">
-        <v>3.776460461218661E-12</v>
+        <v>5.575806426307711E-12</v>
       </c>
       <c r="H2">
-        <v>2.288773017917413E-11</v>
+        <v>3.379308269560472E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.777844839370978E-08</v>
+        <v>1.009981968052069E-07</v>
       </c>
       <c r="C3">
-        <v>9.839875902409862E-08</v>
+        <v>1.662070975164268E-07</v>
       </c>
       <c r="D3">
-        <v>2.163784434573325E-07</v>
+        <v>3.64827530241625E-07</v>
       </c>
       <c r="E3">
-        <v>3.770587133950385E-07</v>
+        <v>5.3445055601004E-07</v>
       </c>
       <c r="F3">
-        <v>1.498737122143493E-06</v>
+        <v>3.03439433930109E-06</v>
       </c>
       <c r="G3">
-        <v>0.08862377627639684</v>
+        <v>0.09185613494241382</v>
       </c>
       <c r="H3">
-        <v>0.3782637724589045</v>
+        <v>0.3110689364322005</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5.761168113684705E-08</v>
+        <v>8.584846728628028E-08</v>
       </c>
       <c r="C4">
-        <v>8.363894518240703E-08</v>
+        <v>1.412760328977646E-07</v>
       </c>
       <c r="D4">
-        <v>1.839216769507175E-07</v>
+        <v>3.101034007142282E-07</v>
       </c>
       <c r="E4">
-        <v>3.204999063978814E-07</v>
+        <v>4.5428297261748E-07</v>
       </c>
       <c r="F4">
-        <v>1.273926553834025E-06</v>
+        <v>2.579235188414839E-06</v>
       </c>
       <c r="G4">
-        <v>0.07533020983490725</v>
+        <v>0.07807771470104771</v>
       </c>
       <c r="H4">
-        <v>0.321524206590023</v>
+        <v>0.2644085959673629</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.03771372188595275</v>
+        <v>0.03680636609138373</v>
       </c>
       <c r="D5">
-        <v>0.03825411244877206</v>
+        <v>0.03826542501705589</v>
       </c>
       <c r="E5">
-        <v>0.03823378474810519</v>
+        <v>0.03824875830673967</v>
       </c>
       <c r="F5">
-        <v>0.03822688182635967</v>
+        <v>0.03824105182611884</v>
       </c>
       <c r="G5">
-        <v>0.03820921721883126</v>
+        <v>0.03826160134454103</v>
       </c>
       <c r="H5">
-        <v>0.03834483656414248</v>
+        <v>0.03839059778387173</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.005157547558002371</v>
+        <v>0.004699219521053125</v>
       </c>
       <c r="C7">
-        <v>0.1130967022386887</v>
+        <v>0.1100372675121437</v>
       </c>
       <c r="D7">
-        <v>0.1148888879910925</v>
+        <v>0.1148888821393482</v>
       </c>
       <c r="E7">
-        <v>0.1148472221853958</v>
+        <v>0.1148472221103156</v>
       </c>
       <c r="F7">
-        <v>0.1148055554586956</v>
+        <v>0.1148055553498342</v>
       </c>
       <c r="G7">
-        <v>0.1146527774299077</v>
+        <v>0.1146527772352793</v>
       </c>
       <c r="H7">
-        <v>0.1144999974842639</v>
+        <v>0.1144999965624379</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.001803338303263921</v>
+        <v>0.001643083743114356</v>
       </c>
       <c r="C9">
-        <v>0.00183057959416063</v>
+        <v>0.001668202965929146</v>
       </c>
       <c r="D9">
-        <v>0.001916827405391517</v>
+        <v>0.00190551278967591</v>
       </c>
       <c r="E9">
-        <v>0.001922586641184125</v>
+        <v>0.001907613054289757</v>
       </c>
       <c r="F9">
-        <v>0.001914920775395048</v>
+        <v>0.001900750734622267</v>
       </c>
       <c r="G9">
-        <v>0.001879166488836194</v>
+        <v>0.001826782290740259</v>
       </c>
       <c r="H9">
-        <v>0.001690127536149768</v>
+        <v>0.001644365967841326</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>2.061033886242091E-07</v>
+        <v>3.112209068211996E-07</v>
       </c>
       <c r="D10">
-        <v>2.007623603068737E-07</v>
+        <v>3.159279185811588E-07</v>
       </c>
       <c r="E10">
-        <v>1.897853063662177E-07</v>
+        <v>2.948281230997338E-07</v>
       </c>
       <c r="F10">
-        <v>1.459366506359325E-07</v>
+        <v>2.272254054936711E-07</v>
       </c>
       <c r="G10">
-        <v>1.348670653500786E-07</v>
+        <v>2.098965659710919E-07</v>
       </c>
       <c r="H10">
-        <v>4.520324176598706E-07</v>
+        <v>6.766237339364087E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.001906271401511</v>
+        <v>1.00190627382394</v>
       </c>
       <c r="C14">
-        <v>1.017726400529315</v>
+        <v>1.01772638094067</v>
       </c>
       <c r="D14">
-        <v>1.011599060372044</v>
+        <v>0.9697975248852796</v>
       </c>
       <c r="E14">
-        <v>1.113116273976636</v>
+        <v>1.107277096538025</v>
       </c>
       <c r="F14">
-        <v>1.334510640805487</v>
+        <v>1.320881211617193</v>
       </c>
       <c r="G14">
-        <v>1.611953024136519</v>
+        <v>1.611953054872131</v>
       </c>
       <c r="H14">
-        <v>2.091586723200068</v>
+        <v>2.091586909961745</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1.357503261190157E-07</v>
+        <v>2.282872006338442E-07</v>
       </c>
       <c r="C19">
-        <v>1.529422791587935E-07</v>
+        <v>2.683672277183357E-07</v>
       </c>
       <c r="D19">
-        <v>2.270656473589737E-07</v>
+        <v>4.015914587905679E-07</v>
       </c>
       <c r="E19">
-        <v>3.937055600696669E-07</v>
+        <v>6.099082377629301E-07</v>
       </c>
       <c r="F19">
-        <v>1.036500928854303E-06</v>
+        <v>2.00764838654874E-06</v>
       </c>
       <c r="G19">
-        <v>1.84265512661548E-06</v>
+        <v>3.233918308066711E-06</v>
       </c>
       <c r="H19">
-        <v>1.385005861775981E-05</v>
+        <v>2.315800706271001E-05</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1.086002608986508E-07</v>
+        <v>1.826297605101471E-07</v>
       </c>
       <c r="C21">
-        <v>1.223538233270348E-07</v>
+        <v>2.146937821746687E-07</v>
       </c>
       <c r="D21">
-        <v>1.816525178871789E-07</v>
+        <v>3.212731670324544E-07</v>
       </c>
       <c r="E21">
-        <v>3.149644480557338E-07</v>
+        <v>4.879265902103437E-07</v>
       </c>
       <c r="F21">
-        <v>8.292007430834427E-07</v>
+        <v>1.606118709238993E-06</v>
       </c>
       <c r="G21">
-        <v>1.474124101292384E-06</v>
+        <v>2.587134646453371E-06</v>
       </c>
       <c r="H21">
-        <v>1.108004689420785E-05</v>
+        <v>1.852640565016802E-05</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.251304660033037E-08</v>
+        <v>1.824250529514188E-08</v>
       </c>
       <c r="C24">
-        <v>3.528879710780153E-07</v>
+        <v>5.324184297194155E-07</v>
       </c>
       <c r="D24">
-        <v>3.431143128424911E-07</v>
+        <v>5.392259984403834E-07</v>
       </c>
       <c r="E24">
-        <v>3.250546778500313E-07</v>
+        <v>5.041399898965554E-07</v>
       </c>
       <c r="F24">
-        <v>2.521277296512955E-07</v>
+        <v>3.916075503123907E-07</v>
       </c>
       <c r="G24">
-        <v>2.360329205429302E-07</v>
+        <v>3.661956368845389E-07</v>
       </c>
       <c r="H24">
-        <v>8.191109861400089E-07</v>
+        <v>1.224649275948312E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>4.488571618542019E-09</v>
+        <v>6.54351414788657E-09</v>
       </c>
       <c r="C25">
-        <v>2.379978936562717E-09</v>
+        <v>3.431890955083374E-09</v>
       </c>
       <c r="D25">
-        <v>2.811041743729183E-09</v>
+        <v>4.168028606782032E-09</v>
       </c>
       <c r="E25">
-        <v>3.587070714563188E-09</v>
+        <v>5.276091352149148E-09</v>
       </c>
       <c r="F25">
-        <v>4.055683578156504E-09</v>
+        <v>5.971450072043108E-09</v>
       </c>
       <c r="G25">
-        <v>4.826510607799253E-09</v>
+        <v>7.101180739598181E-09</v>
       </c>
       <c r="H25">
-        <v>2.77927037917477E-08</v>
+        <v>4.108890025337048E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>7.446138173468052E-09</v>
+        <v>1.064188420568514E-08</v>
       </c>
       <c r="D27">
-        <v>2.366394786155542E-08</v>
+        <v>3.414999869949049E-08</v>
       </c>
       <c r="E27">
-        <v>6.457782308000628E-08</v>
+        <v>8.62383903249897E-08</v>
       </c>
       <c r="F27">
-        <v>2.00915729854091E-07</v>
+        <v>2.541091151468869E-07</v>
       </c>
       <c r="G27">
-        <v>5.330570166553209E-07</v>
+        <v>6.195676553376203E-07</v>
       </c>
       <c r="H27">
-        <v>1.116189135053103E-05</v>
+        <v>9.358622526218399E-06</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>1.242413722971604E-08</v>
+        <v>1.51888127661012E-08</v>
       </c>
       <c r="D30">
-        <v>7.436877535598203E-08</v>
+        <v>9.909776795300357E-08</v>
       </c>
       <c r="E30">
-        <v>0.0287826533526112</v>
+        <v>0.01423347833158775</v>
       </c>
       <c r="F30">
-        <v>0.05187966422178129</v>
+        <v>0.04083989982594861</v>
       </c>
       <c r="G30">
-        <v>0.09791348146276854</v>
+        <v>0.08158997029383902</v>
       </c>
       <c r="H30">
-        <v>0.2413653670374777</v>
+        <v>0.1940422652100115</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.08200689242632067</v>
+        <v>0.08109313023597597</v>
       </c>
       <c r="C31">
-        <v>0.08240436730745287</v>
+        <v>0.08144565216415357</v>
       </c>
       <c r="D31">
-        <v>0.0843662704502581</v>
+        <v>0.08413551341458365</v>
       </c>
       <c r="E31">
-        <v>0.083473870067249</v>
+        <v>0.08400473293630988</v>
       </c>
       <c r="F31">
-        <v>0.08225265421737234</v>
+        <v>0.08251605644474776</v>
       </c>
       <c r="G31">
-        <v>0.08030469021879648</v>
+        <v>0.08064055082684182</v>
       </c>
       <c r="H31">
-        <v>0.07464829810713537</v>
+        <v>0.07499910422647928</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>3.172049832429282E-08</v>
+        <v>5.349241984509132E-08</v>
       </c>
       <c r="D32">
-        <v>0.1068137711455643</v>
+        <v>0.1486153114788251</v>
       </c>
       <c r="E32">
-        <v>0.2213873189875823</v>
+        <v>0.2273441216567244</v>
       </c>
       <c r="F32">
-        <v>0.2802877574958026</v>
+        <v>0.2940078626915348</v>
       </c>
       <c r="G32">
-        <v>0.3009670115945872</v>
+        <v>0.3009669958606205</v>
       </c>
       <c r="H32">
-        <v>0.300966841380448</v>
+        <v>0.3009667441574412</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.003782793246352679</v>
+        <v>0.003782790838984399</v>
       </c>
       <c r="C33">
-        <v>0.003782794061351513</v>
+        <v>0.003782791885835233</v>
       </c>
       <c r="D33">
-        <v>0.003782787994105202</v>
+        <v>0.003782783161055171</v>
       </c>
       <c r="E33">
-        <v>0.003710106745997391</v>
+        <v>0.003592481533787735</v>
       </c>
       <c r="F33">
-        <v>0.00350654086744326</v>
+        <v>0.003415864886712525</v>
       </c>
       <c r="G33">
-        <v>0.003782759874567097</v>
+        <v>0.003782744910891196</v>
       </c>
       <c r="H33">
-        <v>0.003782595814779493</v>
+        <v>0.003782506509345227</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>3.067422359655649E-08</v>
+        <v>4.128044665615205E-08</v>
       </c>
       <c r="D36">
-        <v>3.815324126567131E-08</v>
+        <v>5.448446543873796E-08</v>
       </c>
       <c r="E36">
-        <v>1.003069762913105E-07</v>
+        <v>1.26582465671576E-07</v>
       </c>
       <c r="F36">
-        <v>2.035120462719232E-07</v>
+        <v>2.547001659124542E-07</v>
       </c>
       <c r="G36">
-        <v>2.072331209522199E-07</v>
+        <v>2.736833697603844E-07</v>
       </c>
       <c r="H36">
-        <v>9.735793153585149E-07</v>
+        <v>1.32347769192334E-06</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.1732076351254923</v>
+        <v>0.1642953356781399</v>
       </c>
       <c r="C37">
-        <v>0.173255360433487</v>
+        <v>0.1644661589247197</v>
       </c>
       <c r="D37">
-        <v>0.1844803511803418</v>
+        <v>0.182859836392079</v>
       </c>
       <c r="E37">
-        <v>0.1910674875946145</v>
+        <v>0.1887965506500542</v>
       </c>
       <c r="F37">
-        <v>0.1946053765069518</v>
+        <v>0.1919190514593903</v>
       </c>
       <c r="G37">
-        <v>0.1967209457250048</v>
+        <v>0.1940116709088323</v>
       </c>
       <c r="H37">
-        <v>0.1800263091690655</v>
+        <v>0.1754272071837092</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.06368188107696893</v>
+        <v>0.0735079451220339</v>
       </c>
       <c r="C38">
-        <v>0.06323670854711103</v>
+        <v>0.0729846406448376</v>
       </c>
       <c r="D38">
-        <v>0.05004986236695876</v>
+        <v>0.05190116843855544</v>
       </c>
       <c r="E38">
-        <v>0.0456232986736165</v>
+        <v>0.04759219832743096</v>
       </c>
       <c r="F38">
-        <v>0.04627820101876199</v>
+        <v>0.05157942545108198</v>
       </c>
       <c r="G38">
-        <v>0.04687016511793908</v>
+        <v>0.04845842210774176</v>
       </c>
       <c r="H38">
-        <v>0.08723130515303615</v>
+        <v>0.08736759632371828</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>2.035287745127255E-07</v>
+        <v>3.29285397439051E-07</v>
       </c>
       <c r="C40">
-        <v>2.513410381828921E-07</v>
+        <v>4.345743252347625E-07</v>
       </c>
       <c r="D40">
-        <v>4.434440908163062E-07</v>
+        <v>7.664189890321929E-07</v>
       </c>
       <c r="E40">
-        <v>7.707642734647055E-07</v>
+        <v>1.14435879377297E-06</v>
       </c>
       <c r="F40">
-        <v>2.535238050997796E-06</v>
+        <v>5.042042725849829E-06</v>
       </c>
       <c r="G40">
-        <v>0.08862561893152346</v>
+        <v>0.09185936886072188</v>
       </c>
       <c r="H40">
-        <v>0.3782776225175223</v>
+        <v>0.3110920944392632</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>1.662119420354979E-07</v>
+        <v>2.684782277964273E-07</v>
       </c>
       <c r="C41">
-        <v>2.059927685094418E-07</v>
+        <v>3.559698150724333E-07</v>
       </c>
       <c r="D41">
-        <v>3.655741948378965E-07</v>
+        <v>6.313765677466826E-07</v>
       </c>
       <c r="E41">
-        <v>6.354643544536151E-07</v>
+        <v>9.422095628278237E-07</v>
       </c>
       <c r="F41">
-        <v>2.103127296917468E-06</v>
+        <v>4.185353897653831E-06</v>
       </c>
       <c r="G41">
-        <v>0.07533168395900854</v>
+        <v>0.07808030183569417</v>
       </c>
       <c r="H41">
-        <v>0.3215352866369172</v>
+        <v>0.264427122373013</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-3.731683247722759E-08</v>
+        <v>-6.08071696426237E-08</v>
       </c>
       <c r="C42">
-        <v>-4.534826967345031E-08</v>
+        <v>-7.860451016232913E-08</v>
       </c>
       <c r="D42">
-        <v>-7.786989597840975E-08</v>
+        <v>-1.350424212855103E-07</v>
       </c>
       <c r="E42">
-        <v>-1.352999190110903E-07</v>
+        <v>-2.021492309451463E-07</v>
       </c>
       <c r="F42">
-        <v>-4.321107540803283E-07</v>
+        <v>-8.566888281959978E-07</v>
       </c>
       <c r="G42">
-        <v>-0.01329393497251492</v>
+        <v>-0.01377906702502771</v>
       </c>
       <c r="H42">
-        <v>-0.05674233588060512</v>
+        <v>-0.04666497206625014</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.7653355051681069</v>
+        <v>0.7753218452944223</v>
       </c>
       <c r="C43">
-        <v>0.7432920841862668</v>
+        <v>0.7541096238044354</v>
       </c>
       <c r="D43">
-        <v>0.7232261158083068</v>
+        <v>0.6824226507483129</v>
       </c>
       <c r="E43">
-        <v>0.7923523273080336</v>
+        <v>0.8026831443078011</v>
       </c>
       <c r="F43">
-        <v>0.9928659320409785</v>
+        <v>0.9924212755149709</v>
       </c>
       <c r="G43">
-        <v>1.24311557858834</v>
+        <v>1.262297437228773</v>
       </c>
       <c r="H43">
-        <v>1.654926949214525</v>
+        <v>1.696422389742072</v>
       </c>
     </row>
     <row r="44" spans="1:8">
